--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Locations analyzed</t>
   </si>
   <si>
-    <t xml:space="preserve">Census Units defined by FIPS code</t>
+    <t xml:space="preserve">Selected Locations</t>
   </si>
   <si>
     <t xml:space="preserve">Distance in miles</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">Distance type</t>
   </si>
   <si>
-    <t xml:space="preserve">Miles radius of circular buffer (or distance used if buffering around polygons)</t>
+    <t xml:space="preserve">Residents within any of the 2 specified cities. Area in Square Miles: 88.36</t>
   </si>
   <si>
     <t xml:space="preserve">Population at x% of sites</t>
   </si>
   <si>
-    <t xml:space="preserve">0% of places account for 50% of the total population (approx.)</t>
+    <t xml:space="preserve">The most-populated 50% of the 2 places can account for at least 50% of the total population of all sites as a whole.</t>
   </si>
   <si>
     <t xml:space="preserve">Population at N sites</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743000&amp;buffer=0&amp;sitenumber=-1&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.9634699531927,-93.2677936369264", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743000&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.963469953193,-93.2677936369265", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">2743000</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">Minnesota</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743306&amp;buffer=0&amp;sitenumber=-1&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.9355319808696,-93.7107081310233", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743306&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.9355319808697,-93.7107081310232", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">2743306</t>
@@ -5957,7 +5957,7 @@
         <v>0.812974644245306</v>
       </c>
       <c r="S2" s="28" t="n">
-        <v>1.08127412769043</v>
+        <v>1.08127412769044</v>
       </c>
       <c r="T2" s="28" t="n">
         <v>0.601493907545558</v>
@@ -6041,7 +6041,7 @@
         <v>1.3170152917016</v>
       </c>
       <c r="AU2" s="28" t="n">
-        <v>1.41815394218697</v>
+        <v>1.41815394218698</v>
       </c>
       <c r="AV2" s="28" t="n">
         <v>2.20653957742285</v>
@@ -7141,7 +7141,7 @@
         <v>127.278893976343</v>
       </c>
       <c r="PE2" s="25" t="n">
-        <v>100.365437071176</v>
+        <v>100.365437071175</v>
       </c>
       <c r="PF2" s="25" t="n">
         <v>134.861992779648</v>
@@ -7165,7 +7165,7 @@
         <v>173.449621144755</v>
       </c>
       <c r="PM2" s="25" t="n">
-        <v>44.1921717053729</v>
+        <v>44.192171705373</v>
       </c>
       <c r="PN2" s="25" t="n">
         <v>165.50400143161</v>
@@ -7279,7 +7279,7 @@
         <v>148.045637607575</v>
       </c>
       <c r="QY2" s="23" t="n">
-        <v>57.3795365809011</v>
+        <v>57.3795365809129</v>
       </c>
     </row>
     <row r="3">
@@ -7416,7 +7416,7 @@
         <v>0.342210758140575</v>
       </c>
       <c r="AU3" s="28" t="n">
-        <v>0.537910179587159</v>
+        <v>0.537910179587158</v>
       </c>
       <c r="AV3" s="28" t="n">
         <v>0.160422268053344</v>
@@ -7437,7 +7437,7 @@
         <v>0.23144979948895</v>
       </c>
       <c r="BB3" s="28" t="n">
-        <v>0.0965414570879532</v>
+        <v>0.0965414570879531</v>
       </c>
       <c r="BC3" s="28" t="n">
         <v>0.0259959422919436</v>
@@ -7503,7 +7503,7 @@
         <v>0.313333788166709</v>
       </c>
       <c r="BX3" s="28" t="n">
-        <v>0.805854765268448</v>
+        <v>0.805854765268447</v>
       </c>
       <c r="BY3" s="30" t="n">
         <v>0.363895727164223</v>
@@ -8519,7 +8519,7 @@
         <v>7.07557891337977</v>
       </c>
       <c r="PF3" s="25" t="n">
-        <v>24.1479683249791</v>
+        <v>24.147968324979</v>
       </c>
       <c r="PG3" s="25" t="n">
         <v>9.42138859407052</v>
@@ -8654,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="QY3" s="23" t="n">
-        <v>30.9768218053203</v>
+        <v>30.9768218053251</v>
       </c>
     </row>
   </sheetData>
@@ -10523,7 +10523,7 @@
         <v>1.43296505903985</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>2.11739173358115</v>
+        <v>2.11739173358114</v>
       </c>
       <c r="BN2" s="28" t="n">
         <v>1.26360477486346</v>
@@ -10664,7 +10664,7 @@
         <v>0.00748251633940476</v>
       </c>
       <c r="DH2" s="30" t="n">
-        <v>0.00309425256640238</v>
+        <v>0.00309425256640237</v>
       </c>
       <c r="DI2" s="30" t="n">
         <v>0.0108971534326254</v>
@@ -11542,7 +11542,7 @@
         <v>0.000372222120103671</v>
       </c>
       <c r="OV2" s="30" t="n">
-        <v>0.0439176148374171</v>
+        <v>0.043917614837417</v>
       </c>
       <c r="OW2" s="30" t="n">
         <v>0.0766915427458045</v>
@@ -11707,7 +11707,7 @@
         <v>146.30794436588</v>
       </c>
       <c r="QY2" s="23" t="n">
-        <v>88.3563583862214</v>
+        <v>88.356358386238</v>
       </c>
     </row>
   </sheetData>

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">area_sqmi</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejanalysis.com", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejanalysis.com" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://pedp-ejscreen.azurewebsites.net/index.html</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743000&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.963469953193,-93.2677936369265", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743000&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.963469953193,-93.2677936369265" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">2743000</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">Minnesota</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743306&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.9355319808697,-93.7107081310232", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=2743306&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=44.9355319808697,-93.7107081310232" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">2743306</t>

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
@@ -5101,8 +5101,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
-    <numFmt numFmtId="167" formatCode="#,###,###"/>
+  <numFmts count="12">
+    <numFmt numFmtId="168" formatCode="#,###,###"/>
     <numFmt numFmtId="169" formatCode="#,###,##0.0"/>
     <numFmt numFmtId="171" formatCode="#,###,##0.00"/>
     <numFmt numFmtId="172" formatCode="#,###,##0.000"/>
@@ -5111,8 +5111,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.0"/>
     <numFmt numFmtId="176" formatCode="#0"/>
     <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="#,###,###"/>
-    <numFmt numFmtId="179" formatCode="$#,##0"/>
+    <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,###,###"/>
+    <numFmt numFmtId="180" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -5270,7 +5271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5342,7 +5343,7 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -5353,6 +5354,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8102,7 +8104,7 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="35" t="n">
         <v>426877</v>
       </c>
       <c r="G2"/>
@@ -8582,7 +8584,7 @@
       <c r="FK2" s="33" t="n">
         <v>0.487763454109732</v>
       </c>
-      <c r="FL2" s="35" t="n">
+      <c r="FL2" s="36" t="n">
         <v>48373.2675548226</v>
       </c>
       <c r="FM2" s="33" t="n">
@@ -8663,13 +8665,13 @@
       <c r="GL2" s="33" t="n">
         <v>0.194503376065199</v>
       </c>
-      <c r="GM2" s="33" t="n">
+      <c r="GM2" s="34" t="n">
         <v>3.73293969925763</v>
       </c>
-      <c r="GN2" s="27" t="n">
+      <c r="GN2" s="34" t="n">
         <v>10.2740571640074</v>
       </c>
-      <c r="GO2" s="27" t="n">
+      <c r="GO2" s="34" t="n">
         <v>4.43508575069634</v>
       </c>
       <c r="GP2" s="25" t="n">
@@ -9080,13 +9082,13 @@
       <c r="LU2" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV2" s="33" t="n">
+      <c r="LV2" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW2" s="25" t="n">
+      <c r="LW2" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX2" s="26" t="n">
+      <c r="LX2" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY2" s="33" t="n">
@@ -9197,13 +9199,13 @@
       <c r="NH2" s="33" t="n">
         <v>0.173092206559966</v>
       </c>
-      <c r="NI2" s="33" t="n">
+      <c r="NI2" s="34" t="n">
         <v>5.19868193604147</v>
       </c>
-      <c r="NJ2" s="26" t="n">
+      <c r="NJ2" s="34" t="n">
         <v>9.54753673293002</v>
       </c>
-      <c r="NK2" s="26" t="n">
+      <c r="NK2" s="34" t="n">
         <v>6.69461970613658</v>
       </c>
       <c r="NL2" s="33" t="n">
@@ -10145,7 +10147,7 @@
       <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="34" t="n">
+      <c r="F3" s="35" t="n">
         <v>8347</v>
       </c>
       <c r="G3"/>
@@ -10625,7 +10627,7 @@
       <c r="FK3" s="33" t="n">
         <v>0.509883790583443</v>
       </c>
-      <c r="FL3" s="35" t="n">
+      <c r="FL3" s="36" t="n">
         <v>69670.946088415</v>
       </c>
       <c r="FM3" s="33" t="n">
@@ -10706,13 +10708,13 @@
       <c r="GL3" s="33" t="n">
         <v>0.139487179487179</v>
       </c>
-      <c r="GM3" s="33" t="n">
+      <c r="GM3" s="34" t="n">
         <v>3.6</v>
       </c>
-      <c r="GN3" s="27" t="n">
+      <c r="GN3" s="34" t="n">
         <v>8.8</v>
       </c>
-      <c r="GO3" s="27" t="n">
+      <c r="GO3" s="34" t="n">
         <v>5.9</v>
       </c>
       <c r="GP3" s="25" t="n">
@@ -11123,13 +11125,13 @@
       <c r="LU3" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV3" s="33" t="n">
+      <c r="LV3" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW3" s="25" t="n">
+      <c r="LW3" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX3" s="26" t="n">
+      <c r="LX3" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY3" s="33" t="n">
@@ -11240,13 +11242,13 @@
       <c r="NH3" s="33" t="n">
         <v>0.173092206559966</v>
       </c>
-      <c r="NI3" s="33" t="n">
+      <c r="NI3" s="34" t="n">
         <v>5.19868193604147</v>
       </c>
-      <c r="NJ3" s="26" t="n">
+      <c r="NJ3" s="34" t="n">
         <v>9.54753673293002</v>
       </c>
-      <c r="NK3" s="26" t="n">
+      <c r="NK3" s="34" t="n">
         <v>6.69461970613658</v>
       </c>
       <c r="NL3" s="33" t="n">
@@ -15277,7 +15279,7 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="35" t="n">
         <v>435224</v>
       </c>
       <c r="G2"/>
@@ -15753,7 +15755,7 @@
       <c r="FK2" s="33" t="n">
         <v>0.488187691855229</v>
       </c>
-      <c r="FL2" s="35" t="n">
+      <c r="FL2" s="36" t="n">
         <v>48781.7278481885</v>
       </c>
       <c r="FM2" s="33" t="n">
@@ -15834,13 +15836,13 @@
       <c r="GL2" s="33" t="n">
         <v>0.193220784985304</v>
       </c>
-      <c r="GM2" s="33" t="n">
+      <c r="GM2" s="34" t="n">
         <v>3.73039009797254</v>
       </c>
-      <c r="GN2" s="27" t="n">
+      <c r="GN2" s="34" t="n">
         <v>10.2457867672739</v>
       </c>
-      <c r="GO2" s="27" t="n">
+      <c r="GO2" s="34" t="n">
         <v>4.463180798853</v>
       </c>
       <c r="GP2" s="25" t="n">
@@ -16251,13 +16253,13 @@
       <c r="LU2" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV2" s="33" t="n">
+      <c r="LV2" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW2" s="25" t="n">
+      <c r="LW2" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX2" s="26" t="n">
+      <c r="LX2" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY2" s="33" t="n">
@@ -16368,13 +16370,13 @@
       <c r="NH2" s="33" t="n">
         <v>0.173092206559966</v>
       </c>
-      <c r="NI2" s="33" t="n">
+      <c r="NI2" s="34" t="n">
         <v>5.19868193604147</v>
       </c>
-      <c r="NJ2" s="26" t="n">
+      <c r="NJ2" s="34" t="n">
         <v>9.54753673293002</v>
       </c>
-      <c r="NK2" s="26" t="n">
+      <c r="NK2" s="34" t="n">
         <v>6.69461970613658</v>
       </c>
       <c r="NL2" s="33" t="n">

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_fips_cities.xlsx
@@ -5102,18 +5102,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="12">
-    <numFmt numFmtId="168" formatCode="#,###,###"/>
-    <numFmt numFmtId="169" formatCode="#,###,##0.0"/>
-    <numFmt numFmtId="171" formatCode="#,###,##0.00"/>
-    <numFmt numFmtId="172" formatCode="#,###,##0.000"/>
+    <numFmt numFmtId="167" formatCode="#,###,###"/>
+    <numFmt numFmtId="168" formatCode="#,###,##0.0"/>
+    <numFmt numFmtId="170" formatCode="#,###,##0.00"/>
+    <numFmt numFmtId="171" formatCode="#,###,##0.000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00"/>
     <numFmt numFmtId="173" formatCode="#,##0.00"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00"/>
-    <numFmt numFmtId="175" formatCode="#,##0.0"/>
-    <numFmt numFmtId="176" formatCode="#0"/>
-    <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
-    <numFmt numFmtId="179" formatCode="#,###,###"/>
-    <numFmt numFmtId="180" formatCode="$#,##0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
+    <numFmt numFmtId="175" formatCode="#0"/>
+    <numFmt numFmtId="176" formatCode="0%"/>
+    <numFmt numFmtId="177" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,###,###"/>
+    <numFmt numFmtId="179" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -5343,8 +5343,9 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -5354,7 +5355,6 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
